--- a/output/pdf_financials_xlsx/THX.xlsx
+++ b/output/pdf_financials_xlsx/THX.xlsx
@@ -6317,37 +6317,37 @@
         <v>0</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>-0.052167</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>0.07857500000000001</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>0.813671</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>0.782249</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>1.793362</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0</v>
+        <v>0.488362</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>0.6931040000000001</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0</v>
+        <v>1.341031</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0</v>
+        <v>0.559126</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>0</v>
+        <v>-0.769689</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>0</v>
+        <v>-3.739985</v>
       </c>
       <c r="P91" s="3" t="n">
         <v>0</v>
@@ -6358,10 +6358,10 @@
         </is>
       </c>
       <c r="R91" s="3" t="n">
-        <v>0</v>
+        <v>-3.873</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>0</v>
+        <v>-4.247</v>
       </c>
     </row>
     <row r="92">
@@ -6380,25 +6380,25 @@
         <v>1.360308</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.539308</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.539308</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.539308</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.539308</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.539308</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.539308</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.582308</v>
       </c>
       <c r="L92" s="3" t="n">
         <v>0</v>
@@ -8004,43 +8004,43 @@
         <v>1e-06</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.486513</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-2.139554</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-1.102738</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.392637</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.127738</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.100513</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-2.930111</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-5.725747</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-0.23889</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>-0.267611</v>
+        <v>-2.29497</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>-0.093027</v>
+        <v>-2.741758</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-5.366778</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-9.409107000000001</v>
       </c>
       <c r="R118" s="1" t="inlineStr">
         <is>
@@ -11970,7 +11970,11 @@
           <t>Currency translation reserve 16</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -18808,7 +18812,11 @@
           <t>Currency translation reserve</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -23018,7 +23026,11 @@
           <t>Reserve 12</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -23728,7 +23740,11 @@
           <t>Reserve 13</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -24900,7 +24916,11 @@
           <t>Reserve 11</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -26406,7 +26426,11 @@
           <t>Reserves 12 1,539,308</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
@@ -30618,7 +30642,11 @@
           <t>Exploration &amp; Evaluation assets expenditures 15</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>-</t>
@@ -34402,7 +34430,11 @@
           <t>Exploration &amp; Evaluation assets expenditures 16</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
@@ -37160,7 +37192,11 @@
           <t>Exploration and evaluation expenditures 16</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -40096,7 +40132,11 @@
           <t>Exploration and evaluation expenditures 10</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>
@@ -41448,7 +41488,11 @@
           <t>Exploration and evaluation expenditures 9</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
           <t>-</t>
@@ -43524,7 +43568,11 @@
           <t>Exploration and evaluation expenditures 10</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr"/>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E329" t="inlineStr">
         <is>
           <t>-</t>
@@ -47112,7 +47160,11 @@
           <t>Exploration and evaluation expenditures 9</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr"/>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E363" t="inlineStr">
         <is>
           <t>-</t>
@@ -56188,7 +56240,7 @@
         <v>-2.069195</v>
       </c>
       <c r="S448" s="5" t="n">
-        <v>25.398941</v>
+        <v>-25.398941</v>
       </c>
       <c r="T448" t="inlineStr">
         <is>
@@ -56296,7 +56348,7 @@
         <v>-2.069195</v>
       </c>
       <c r="S449" s="5" t="n">
-        <v>25.398941</v>
+        <v>-25.398941</v>
       </c>
       <c r="T449" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/THX.xlsx
+++ b/output/pdf_financials_xlsx/THX.xlsx
@@ -1101,22 +1101,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.057939</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.026775</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.022021</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.028201</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.001819</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>7.6e-05</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -2166,22 +2166,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.316781</v>
+        <v>-0.37472</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.40863</v>
+        <v>-0.435405</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.075652</v>
+        <v>-0.097673</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.929033</v>
+        <v>-0.957234</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.259943</v>
+        <v>-1.261762</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.82872</v>
+        <v>-0.828796</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-0.426853</v>
@@ -2296,22 +2296,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.316781</v>
+        <v>-0.37472</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.40863</v>
+        <v>-0.435405</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.075652</v>
+        <v>-0.097673</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.929033</v>
+        <v>-0.957234</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.258868</v>
+        <v>-1.260687</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.827008</v>
+        <v>-0.827084</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-0.424886</v>
@@ -2619,49 +2619,49 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.101444</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.013416</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.013416</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.149195</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.199874</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.30658</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.080474</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.166981</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.469015</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.239605</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.304067</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>5.40292</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>28.261552</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>22.181737</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>1.27627</v>
       </c>
       <c r="Q34" s="1" t="inlineStr">
         <is>
@@ -2669,10 +2669,10 @@
         </is>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>12.04</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>137.75</v>
       </c>
     </row>
     <row r="35">
@@ -2745,49 +2745,49 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>1.600082</v>
+        <v>1.701526</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>2.950153</v>
+        <v>2.963569</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>2.950153</v>
+        <v>2.963569</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1.4437</v>
+        <v>2.592895</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.199874</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.30658</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.080474</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.166981</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.469015</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.239605</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.304067</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>5.40292</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>28.261552</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>22.181737</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>1.27627</v>
       </c>
       <c r="Q36" s="1" t="inlineStr">
         <is>
@@ -2795,10 +2795,10 @@
         </is>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>12.04</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>137.75</v>
       </c>
     </row>
     <row r="37">
@@ -3501,49 +3501,49 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.158752</v>
+        <v>0.057308</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.060195</v>
+        <v>0.046779</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.023767</v>
+        <v>0.010351</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.251991</v>
+        <v>0.052117</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.34085</v>
+        <v>0.03427</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.106816</v>
+        <v>0.026342</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.179182</v>
+        <v>0.012201</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.561741</v>
+        <v>0.092726</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.291593</v>
+        <v>0.051988</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.442044</v>
+        <v>0.137977</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>5.603269</v>
+        <v>0.200349</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>33.274274</v>
+        <v>5.012722</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>3.04291</v>
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>5.359127</v>
+        <v>4.082857</v>
       </c>
       <c r="Q48" s="1" t="inlineStr">
         <is>
@@ -3551,10 +3551,10 @@
         </is>
       </c>
       <c r="R48" s="3" t="n">
-        <v>12.04</v>
+        <v>0</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>137.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -9422,7 +9422,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -12892,7 +12892,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -16308,7 +16308,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -22316,7 +22316,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
@@ -25130,7 +25130,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -53108,7 +53108,11 @@
           <t>Interest expense 5e</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E419" t="inlineStr">
         <is>
           <t>-</t>
@@ -55626,7 +55630,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
@@ -57868,7 +57872,7 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
@@ -60934,7 +60938,7 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
@@ -62294,7 +62298,7 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
@@ -65988,7 +65992,7 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
@@ -68234,7 +68238,7 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
@@ -68342,7 +68346,7 @@
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
@@ -69832,7 +69836,7 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E578" s="5" t="n">

--- a/output/pdf_financials_xlsx/THX.xlsx
+++ b/output/pdf_financials_xlsx/THX.xlsx
@@ -7620,7 +7620,7 @@
         <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.018515</v>
       </c>
       <c r="H112" s="3" t="n">
         <v>0</v>
@@ -44602,7 +44602,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
